--- a/data/trans_orig/Q5410A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2581,62 +2581,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>579</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24380</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>14700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>14813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33443</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>43922</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>43922</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>43922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>380</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>412</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
